--- a/output/Campus FY 2025-26 annual statistics NZ-level report/2025 - 2026/exclusions tab/UCD_targeted_review_FY2025-26_exclusions_documentation_as_of_2026-07-09.xlsx
+++ b/output/Campus FY 2025-26 annual statistics NZ-level report/2025 - 2026/exclusions tab/UCD_targeted_review_FY2025-26_exclusions_documentation_as_of_2026-07-09.xlsx
@@ -3634,7 +3634,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="55">
       <c r="A55" s="32" t="inlineStr">
         <is>
-          <t>"Portfolio Library Unit"."Library Name" is equal to / is in X_Do_Not_Use_</t>
+          <t>"Portfolio Library Unit"."Library Name" LIKE 'X_Do_Not_Use_%'</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
@@ -5711,7 +5711,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="86">
       <c r="A86" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name" is equal to / is in Ebook Central Perpetual, DDA and Subscription Titles; EBSCO (UCSD). eBook Collection DDA online monographs.; R2 Digital Library DDA</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IN ('Ebook Central Perpetual, DDA and Subscription Titles', 'EBSCO (UCSD). eBook Collection DDA online monographs.', 'R2 Digital Library DDA')</t>
         </is>
       </c>
       <c r="B86" s="39" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="87">
       <c r="A87" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name" is equal to / is in British and Irish Women's Letters and Diaries: First Edition (Pre-January 2009 Purchasers Only); Books@Ovid - LWW JBIB Book Collection 2017-2018 Purchase; Books@Ovid Purchase; Books@Ovid Purchase Complete; North American Indian Drama: First Edition (Pre-October 2012 Purchasers Only); Twentieth Century North American Drama: First Edition (Pre-October 2012 Purchasers Only); Institute of Physics Historic Archive Purchase; Maruzen eBook Library; Berkeley LDC purchases; IGI Global Evidence Based PURCHASED; Oxford University Press Anthropology Local Purchased Collection; Sage EBS; Sage online monographs EBS (Sage EBS) purchased; UC Davis locally purchased monographs_LOCAL; UCSC owned streaming video; African Writers Series (pre-September 2011 purchase); SAGE Complete Deep Backfile Purchase 2008; SAGE Deep Backfile Upgrade Purchase 2009; SAGE Deep Backfile Upgrade Purchase 2010; SAGE Deep Backfile Upgrade Purchase 2011; SAGE Deep Backfile Upgrade Purchase 2012; SAGE Deep Backfile Upgrade Purchase 2013; SAGE Deep Backfile Upgrade Purchase 2014; SAGE Deep Backfile Upgrade Purchase 2015; SAGE Deep Backfile Upgrade Purchase 2016; SAGE Deep Backfile Upgrade Purchase 2017; SAGE Psychology Subject Collection Backfile Purchase; Taylor &amp; Francis online monographs (EBS) purchased</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IN ('British and Irish Women''s Letters and Diaries: First Edition (Pre-January 2009 Purchasers Only)', 'Books@Ovid - LWW JBIB Book Collection 2017-2018 Purchase', 'Books@Ovid Purchase', 'Books@Ovid Purchase Complete', 'North American Indian Drama: First Edition (Pre-October 2012 Purchasers Only)', 'Twentieth Century North American Drama: First Edition (Pre-October 2012 Purchasers Only)', 'Institute of Physics Historic Archive Purchase', 'Maruzen eBook Library', 'Berkeley LDC purchases', 'IGI Global Evidence Based PURCHASED', 'Oxford University Press Anthropology Local Purchased Collection', 'Sage EBS', 'Sage online monographs EBS (Sage EBS) purchased', 'UC Davis locally purchased monographs_LOCAL', 'UCSC owned streaming video', 'African Writers Series (pre-September 2011 purchase)', 'SAGE Complete Deep Backfile Purchase 2008', 'SAGE Deep Backfile Upgrade Purchase 2009', 'SAGE Deep Backfile Upgrade Purchase 2010', 'SAGE Deep Backfile Upgrade Purchase 2011', 'SAGE Deep Backfile Upgrade Purchase 2012', 'SAGE Deep Backfile Upgrade Purchase 2013', 'SAGE Deep Backfile Upgrade Purchase 2014', 'SAGE Deep Backfile Upgrade Purchase 2015', 'SAGE Deep Backfile Upgrade Purchase 2016', 'SAGE Deep Backfile Upgrade Purchase 2017', 'SAGE Psychology Subject Collection Backfile Purchase', 'Taylor &amp; Francis online monographs (EBS) purchased')</t>
         </is>
       </c>
       <c r="B87" s="39" t="inlineStr">
@@ -5845,7 +5845,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="88">
       <c r="A88" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name"</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IS NULL</t>
         </is>
       </c>
       <c r="B88" s="39" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="97">
       <c r="A97" s="32" t="inlineStr">
         <is>
-          <t>"Institution"."Institution Name"3126</t>
+          <t>"Institution"."Institution Name" = 3126</t>
         </is>
       </c>
       <c r="B97" s="39" t="inlineStr">
@@ -10200,7 +10200,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="153">
       <c r="A153" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in ILL; OUT_RS_REQ</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('ILL', 'OUT_RS_REQ')</t>
         </is>
       </c>
       <c r="B153" s="39" t="inlineStr">
@@ -10334,7 +10334,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="155">
       <c r="A155" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in RLIST; RESV; TPREP; CRES; RFRES; RES; SERES</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('RLIST', 'RESV', 'TPREP', 'CRES', 'RFRES', 'RES', 'SERES')</t>
         </is>
       </c>
       <c r="B155" s="39" t="inlineStr">
@@ -10401,7 +10401,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="156">
       <c r="A156" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in BIOET; BMLEX; GAMES; GEN; GRESV; NEW; REF; ARCHV; MRR; MLK; MEDIA; POP; STX; SARES; SHLDS; BIOV; CAMPUS; EAL; EALRF; GVMED; GVSTX; MANNSHREM; MICRO; OVER; ASC; UCDGROWN; PSEL; RARE; SPCOL; SUPSD; EALOV; GENSP</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('BIOET', 'BMLEX', 'GAMES', 'GEN', 'GRESV', 'NEW', 'REF', 'ARCHV', 'MRR', 'MLK', 'MEDIA', 'POP', 'STX', 'SARES', 'SHLDS', 'BIOV', 'CAMPUS', 'EAL', 'EALRF', 'GVMED', 'GVSTX', 'MANNSHREM', 'MICRO', 'OVER', 'ASC', 'UCDGROWN', 'PSEL', 'RARE', 'SPCOL', 'SUPSD', 'EALOV', 'GENSP')</t>
         </is>
       </c>
       <c r="B156" s="39" t="inlineStr">
@@ -10602,7 +10602,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="159">
       <c r="A159" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Faculty and Staff; Law Faculty; UC Ac.Sen., Ac.Fed. &amp; Clin.Fac.(active &amp; retired); UC Research (active &amp; retired); UCD Ac.Sen., Ac.Fed. &amp; Clin.Fac.(active &amp; retired); UCD Research (active &amp; retired)</t>
+          <t>"Borrower Details"."User Group" IN ('Faculty and Staff', 'Law Faculty', 'UC Ac.Sen., Ac.Fed. &amp; Clin.Fac.(active &amp; retired)', 'UC Research (active &amp; retired)', 'UCD Ac.Sen., Ac.Fed. &amp; Clin.Fac.(active &amp; retired)', 'UCD Research (active &amp; retired)')</t>
         </is>
       </c>
       <c r="B159" s="39" t="inlineStr">
@@ -10669,7 +10669,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="160">
       <c r="A160" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Graduate Students; Health Sciences Graduate Students; Health Sciences Residents; Law Students and Staff; UC Graduate; UCD Graduate; UCD Health Sciences Graduate; UCD Health Sciences Resident</t>
+          <t>"Borrower Details"."User Group" IN ('Graduate Students', 'Health Sciences Graduate Students', 'Health Sciences Residents', 'Law Students and Staff', 'UC Graduate', 'UCD Graduate', 'UCD Health Sciences Graduate', 'UCD Health Sciences Resident')</t>
         </is>
       </c>
       <c r="B160" s="39" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="161">
       <c r="A161" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Library Internal; Library Internal - Long Loan; Internal Library Staff; Internal Library Staff -- In-house use; UC Staff (active &amp; retired); UCD Staff (active &amp; retired)</t>
+          <t>"Borrower Details"."User Group" IN ('Library Internal', 'Library Internal - Long Loan', 'Internal Library Staff', 'Internal Library Staff -- In-house use', 'UC Staff (active &amp; retired)', 'UCD Staff (active &amp; retired)')</t>
         </is>
       </c>
       <c r="B161" s="39" t="inlineStr">
@@ -10803,7 +10803,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="162">
       <c r="A162" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Undergraduate students; Special UNEX Student; UC Undergraduate; UCD Honors Undergraduate (UCD only)</t>
+          <t>"Borrower Details"."User Group" IN ('Undergraduate students', 'Special UNEX Student', 'UC Undergraduate', 'UCD Honors Undergraduate (UCD only)')</t>
         </is>
       </c>
       <c r="B162" s="39" t="inlineStr">
@@ -10870,7 +10870,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="163">
       <c r="A163" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Miscellaneous; CA college students; Courtesy -- Alumni; Courtesy 10 limit; Courtesy 50 limit; Fee 5 limit; Problem patrons; Stanford; Suspended Account; Temporary Affiliates; UCD Spouse or Adult Child</t>
+          <t>"Borrower Details"."User Group" IN ('Miscellaneous', 'CA college students', 'Courtesy -- Alumni', 'Courtesy 10 limit', 'Courtesy 50 limit', 'Fee 5 limit', 'Problem patrons', 'Stanford', 'Suspended Account', 'Temporary Affiliates', 'UCD Spouse or Adult Child')</t>
         </is>
       </c>
       <c r="B163" s="39" t="inlineStr">
@@ -10937,7 +10937,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="164">
       <c r="A164" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Alumni and CA Community; Law Visiting Scholars; Law Public</t>
+          <t>"Borrower Details"."User Group" IN ('Alumni and CA Community', 'Law Visiting Scholars', 'Law Public')</t>
         </is>
       </c>
       <c r="B164" s="39" t="inlineStr">
@@ -11004,7 +11004,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="165">
       <c r="A165" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"Network</t>
+          <t>"Borrower Details"."User Group" = 'Network'</t>
         </is>
       </c>
       <c r="B165" s="39" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="166">
       <c r="A166" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in UCD Undergraduate; Test; zPurge Health Sciences Residents (only assign for Purge Job); zPurge Miscellaneous (only assign for Purge Job)</t>
+          <t>"Borrower Details"."User Group" IN ('UCD Undergraduate', 'Test', 'zPurge Health Sciences Residents (only assign for Purge Job)', 'zPurge Miscellaneous (only assign for Purge Job)')</t>
         </is>
       </c>
       <c r="B166" s="39" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="167">
       <c r="A167" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"</t>
+          <t>"Borrower Details"."User Group" IS NULL</t>
         </is>
       </c>
       <c r="B167" s="39" t="inlineStr">
@@ -11205,7 +11205,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="168">
       <c r="A168" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Interlibrary Loan; Interlibrary Loan -- UC Fac/Grad</t>
+          <t>"Borrower Details"."User Group" IN ('Interlibrary Loan', 'Interlibrary Loan -- UC Fac/Grad')</t>
         </is>
       </c>
       <c r="B168" s="39" t="inlineStr">
